--- a/光伏配储项目/电价数据/2026/三江站.xlsx
+++ b/光伏配储项目/电价数据/2026/三江站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.53722</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.24544</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.64391</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.01131</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.82301</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.71746</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44036</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45607</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44051</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42259</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.45385</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40818</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39764</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.39855</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38323</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40147</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42442</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41093</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35281</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.3917</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38414</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41533</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39383</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42639</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41229</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.4223</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41221</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44574</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.47372</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.29785</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.37138</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.76344</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.61286</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.5171399999999999</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.2712</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.39473</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.57168</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.59735</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.26818</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.81884</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.82076</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.82678</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.50173</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.16807</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.54489</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.54237</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.8118</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.93096</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.6014700000000001</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.65401</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.6332100000000001</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.80501</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.7539600000000001</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.8160299999999999</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.05898</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.33085</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.47777</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.73542</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.66144</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.17309</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.98799</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.84641</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.00479</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.19547</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.9536100000000001</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.73849</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.44948</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.16057</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.77677</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.12489</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.21318</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.07193</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.45339</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.19708</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.18019</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.13606</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.7313200000000001</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47934</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40656</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41291</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42214</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.08356</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.96484</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.04673</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53613</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52254</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50624</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.53464</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49785</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.4102</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47236</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38776</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38089</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39203</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33759</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37518</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37515</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42093</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.54947</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.76007</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.72392</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.46009</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.43845</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38894</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.8433200000000001</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.9890399999999999</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.62491</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.8116100000000001</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.85117</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.7518400000000001</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.6412</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.49082</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.5132100000000001</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.6258400000000001</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34578</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.04453</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.07094</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.35276</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37148</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.00339</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.28079</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.87958</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.8001699999999999</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.19869</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.02716</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.93111</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.53494</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.50305</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.59072</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.48391</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.50952</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.12135</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.97116</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.93825</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.9605</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.86256</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.7965800000000001</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.81575</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.59194</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.90047</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.12413</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.05804</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.88502</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.25932</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.49659</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.43725</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.52414</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.62246</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.60617</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.76701</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.10687</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.21275</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.9419099999999999</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.66575</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.6344500000000001</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.78932</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44071</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43473</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41752</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37736</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33348</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51544</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.4709</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.54289</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.4345</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.4406600000000001</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39856</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38904</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38192</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43355</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44946</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39314</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36614</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36291</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35605</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47328</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44988</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44396</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39669</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35162</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36799</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.63091</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.65096</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.81855</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.6645</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.6202300000000001</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.61372</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.47393</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31485</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.30201</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.4975</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.39283</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.69787</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.9262</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.27468</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.6180399999999999</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.9956</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.34078</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.84126</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.8934</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.68992</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.82799</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.9793999999999999</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.96378</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.70239</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.45963</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.38493</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.40895</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.52666</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.93772</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.87452</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.98261</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.55938</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.16922</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.15956</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.98597</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.92662</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.8743500000000001</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.33468</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.27647</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.14047</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.10598</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.16826</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.10126</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.05138</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.56093</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.9262100000000001</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.58711</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.92445</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.94532</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.9313899999999999</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.02873</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.95688</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.06082</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.88395</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.6769299999999999</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.65942</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.5011100000000001</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.38855</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34312</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.9224199999999999</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.58593</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.49567</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.47029</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.52396</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.59099</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.39093</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.57592</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.37346</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.35348</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.46641</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33921</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.37241</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38874</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.33797</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.4206</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.5824199999999999</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.5549400000000001</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.6821799999999999</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.92165</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.9865</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.68196</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.07758</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.12069</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.65374</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.73937</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.01334</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.9993500000000001</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.22736</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.85517</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.9228500000000001</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.55425</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.69824</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.4822</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.43665</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.54079</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.8317899999999999</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.97789</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.82735</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.85461</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.87971</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.8151</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.7752599999999999</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.73921</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.97072</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.02727</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.9855</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.9252400000000001</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.65496</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.8415199999999999</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.88839</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.81667</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.91401</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.9924500000000001</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.01114</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.9743999999999999</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.00413</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.64117</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.9219400000000001</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.88181</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.83597</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.91164</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.94729</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.9427000000000001</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.9154600000000001</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.85725</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.60999</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.45236</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.6180599999999999</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31809</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31203</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.57484</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.46495</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.39933</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32575</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31167</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31363</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31476</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30771</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.3082</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.21713</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.21255</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.2536</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.21227</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.29271</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.23022</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.24695</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.4793</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.39359</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.18123</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.40852</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.17671</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.47687</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.39495</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.17751</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.30415</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.29669</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.25599</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.18335</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.2183</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.20722</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.16562</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.18381</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.19497</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.17433</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.35636</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.39355</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.5184800000000001</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.43156</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.37665</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.42845</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.43787</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.50945</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.4444</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.46452</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.4021</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.45319</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39953</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39845</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40986</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31137</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.02263</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.78189</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.80965</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.5359400000000001</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.51851</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.39596</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.38358</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.35331</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.38341</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.22691</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.06558</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.17234</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04424</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04319</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04185</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01164</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20836</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.0508</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.16006</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.0633</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04274</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04482</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0447</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.01445</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04449</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04193</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04235</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.17057</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04439</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04232</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04347</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.17102</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.17114</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04979</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.17342</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.18476</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.19129</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.19143</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.19375</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.38945</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.42879</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.36308</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.3617</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.39088</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.36881</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.33341</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.38278</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33588</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.38943</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40552</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32172</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.30306</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.30672</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.30185</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30445</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.30173</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.2955</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.29175</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.29807</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.25523</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.24843</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16013</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15937</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23742</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.27352</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.28964</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.29984</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.30533</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.30295</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.30538</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.30515</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.30183</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.30648</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.62748</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.73764</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.57999</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.5535099999999999</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.59999</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.6515</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.8030700000000001</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.48546</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.35421</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.46303</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.64452</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.63979</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.75682</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.51977</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.47276</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.41273</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.40907</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.14166</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.60823</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.6134299999999999</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.55611</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.5442899999999999</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.48022</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.6692100000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79669</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.73956</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.54657</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.67626</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.95584</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.2757</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.7495000000000001</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.29692</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.27019</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.68706</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.6819</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.25592</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.93132</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.64357</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.25622</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.75012</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.65641</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.3389</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.71672</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.80443</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78762</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.78826</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8785700000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8809199999999999</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5057699999999999</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41203</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41615</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46437</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.22326</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6393</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5423600000000001</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50202</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45761</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42593</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43986</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45037</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39227</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45256</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42037</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38803</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.3903</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35061</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.4051</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45066</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.3557</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39089</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.39993</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.59539</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43383</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.5835</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66592</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.8251499999999999</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.5746100000000001</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.55374</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.54503</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.29781</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.8807200000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.15827</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.1352</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.10062</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.47797</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.64983</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.48275</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.47399</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.79388</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.6757000000000001</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5803200000000001</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.52446</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.49173</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.8275</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.6889700000000001</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.41315</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.5424500000000001</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.55516</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.43057</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.5267500000000001</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.5166499999999999</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.54406</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.56323</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.51564</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.54167</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.55599</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.51045</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.54131</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.53743</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.47182</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.5297000000000001</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.5540900000000001</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.64579</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.5424500000000001</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.6370399999999999</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.55572</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.55015</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.5599299999999999</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.53944</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.52647</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.51319</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.5230399999999999</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.45206</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.47011</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41226</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45203</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41462</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39112</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37456</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35303</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.95589</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36057</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.47605</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40682</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.47765</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.5399299999999999</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.39156</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.40938</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.38977</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.40662</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.38164</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.58477</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.39316</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.49202</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.5311399999999999</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.6159</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.72651</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.89864</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.70169</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.43541</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.8212699999999999</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.6966599999999999</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.77603</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.70951</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.5546</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.67574</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.8250599999999999</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.31868</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.44954</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.43597</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.40522</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.73173</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.16303</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.74102</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.5955499999999999</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.9658099999999999</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.6651</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.68096</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.5398999999999999</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.20972</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.62846</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.38106</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.36842</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.40145</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.38248</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.42858</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.40095</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.46957</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.41319</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.41511</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.7465000000000001</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.39375</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.39124</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42043</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35896</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59674</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.08287</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.75467</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.37521</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70356</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79531</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64976</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58361</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42802</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.71009</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.41781</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.64815</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.91376</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.7392799999999999</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.55345</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.12599</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.58605</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.13166</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.37825</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.44756</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.98205</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.18677</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.72733</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.5116700000000001</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.19492</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.03809</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.85482</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.8358</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.81238</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.82074</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.27685</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.09327</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.50885</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.67689</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.0746</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.60777</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.84097</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.82236</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.70126</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.75115</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.72915</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.87875</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.9010199999999999</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.72651</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.9085800000000001</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.18421</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.81672</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.81955</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.91801</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.78174</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.80552</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.16116</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.78692</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.80463</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.87862</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.74954</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.7371599999999999</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.36993</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.9195</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.52284</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.27852</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.82396</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.83497</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.6569199999999999</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38652</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32955</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3247</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.43173</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34391</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39126</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37498</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.37568</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.3563</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.3128</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.27813</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.30373</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.73141</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.6656599999999999</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.24984</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.26654</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.37581</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.39544</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.30583</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.2997</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.28953</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.34337</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.27155</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.5541</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.39076</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36167</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40561</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.3849</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.44951</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.39957</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40187</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39771</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45087</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43927</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44419</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40243</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39029</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39748</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34933</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5423</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38895</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41592</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.3929</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37952</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39075</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34442</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.36985</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37541</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29241</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30532</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.4468</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.27976</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.53047</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.29354</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.27559</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.29904</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.38616</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30491</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.31415</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29752</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.29293</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.41441</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.5482899999999999</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.49255</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.49041</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.6066699999999999</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.83072</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.7778200000000001</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.61372</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.4049700000000001</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.39764</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.54706</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.66969</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.79332</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.77839</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.65847</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.45604</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.41241</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.39525</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.36826</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.3922</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.42963</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.41418</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.39564</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41863</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.49457</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.37439</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.42489</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.58027</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.7290399999999999</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.72919</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.7179</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.72014</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.03213</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.03427</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.65334</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.7712</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.20727</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.69814</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.19141</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.07156</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.06429</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.13165</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.42811</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.83486</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.32015</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.46049</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.8346699999999999</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.79669</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.71112</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.0639</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.04697</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.08041</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.09377</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.08887</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.066</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.09045</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.82659</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.12356</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.34609</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.20499</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.23243</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.12056</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.1283</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.1364</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.07239</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.17068</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.7060700000000001</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.7693300000000001</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.11439</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.12277</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.11665</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.69682</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.19609</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.51302</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.14629</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.28752</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.62573</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.53166</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.41164</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.68981</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.16294</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.74236</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34351</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.41623</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34978</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32916</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.32512</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.43258</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.77239</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32605</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33517</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34593</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33826</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.55169</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.5561699999999999</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.38565</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.57704</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.41859</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.43643</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.43844</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33824</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29311</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34166</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.2829100000000001</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.36976</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.41055</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.6724</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.98034</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.82851</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.6562100000000001</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.56972</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.40187</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.36681</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35006</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.42462</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.43085</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.40855</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.44466</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36763</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36781</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37311</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.3929</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37162</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40289</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36944</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36097</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.3493</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3383</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34947</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34853</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.3398</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29617</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37108</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.39753</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.57611</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.38246</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.43887</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.14016</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.42894</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.38823</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.3407</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.39667</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.56329</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38924</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35461</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.39741</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.41936</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38469</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.55245</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.42177</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.42344</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38363</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42992</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40915</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65191</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83102</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47183</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40133</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45942</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3934</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34477</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41061</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37566</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35357</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3565</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37946</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.35435</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.3965</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.43925</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.3822</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.5808</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.29529</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.5767599999999999</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.1925</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.35928</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.42453</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.27152</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.39303</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.54261</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.41831</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.41408</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.38411</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.74139</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.75002</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.00755</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.8152699999999999</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.68269</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.81656</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.62537</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.85162</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.80071</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.6695399999999999</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.14874</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.70943</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.92134</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.5674</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.02731</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.35492</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.62049</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.42612</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.96304</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.1531</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.9102899999999999</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42977</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.4187</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37769</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37427</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36015</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.6634099999999999</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.17728</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.97209</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41943</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.41751</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.4047</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41092</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40859</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.4175</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.39981</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39548</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41125</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.40898</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39338</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38666</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41823</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38684</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41643</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.39975</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.3997</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41228</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39984</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45039</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44946</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5603899999999999</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50052</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45056</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.47012</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.44445</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.1325</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.68795</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.75914</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.57302</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.5112</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.70175</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.48898</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.53888</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.50762</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.74787</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.81325</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.87988</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.36433</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.73119</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.48295</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.42356</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.34647</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.20235</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.89536</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.76142</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.14749</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.45197</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.50256</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.52597</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.6511</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.93287</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.61215</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.79022</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.59539</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.80862</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.79632</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.3046</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.26478</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.94213</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.94328</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.10184</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.07768</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.45059</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.76283</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.55769</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.12783</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.19765</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.76252</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.96228</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.1686</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.8405499999999999</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47795</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47136</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41937</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.02212</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.6146900000000001</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.48019</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45802</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43676</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42655</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44836</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41783</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45769</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39934</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40705</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39864</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38855</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37487</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38658</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37959</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.43158</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.45655</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.39894</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.50014</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39437</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.4659700000000001</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.61898</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.5918600000000001</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.5923999999999999</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.99111</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.88297</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.26928</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.10695</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.64766</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.69423</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.7049299999999999</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.47379</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.38825</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>1.39664</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.31702</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35262</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.45413</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.44236</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.47695</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.47415</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.44101</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36366</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41294</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.4294</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.50778</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.48897</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.55386</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38311</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40608</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.4025899999999999</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37799</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39925</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37947</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39963</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36027</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37905</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36414</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.64697</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.8580800000000001</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.52976</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.43088</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.41126</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37704</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37702</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.39495</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.37804</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33547</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.3275</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.40262</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.30485</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.30186</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.20387</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.30693</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.26054</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04336</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.20116</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.26048</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.27379</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.21015</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.26252</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.29165</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.28996</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.24864</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.27325</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.3048</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.39024</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.28662</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.41193</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.5295700000000001</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.45264</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.40799</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.44301</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.42132</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.5033299999999999</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.38367</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44709</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.40663</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39943</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.40286</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.38658</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.41946</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.40534</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.44628</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.3649</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.37786</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35167</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.60022</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34897</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31027</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3074</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.30908</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.2053</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.26308</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.38191</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.25486</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.24828</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.20661</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.19047</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.25717</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.18504</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.2046</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.18412</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.22432</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.55069</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.2593</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.24415</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.19617</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.18517</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.21713</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.17871</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.20091</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.18647</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.17894</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.20846</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.42543</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.33757</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.17774</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.18664</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.17776</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.19235</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.18464</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.18793</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.30155</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.23113</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.28848</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.28367</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.35244</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.38206</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.6509199999999999</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.40921</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.3336</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.85527</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.89835</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.43585</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.5003299999999999</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.41813</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.56523</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.53895</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.42588</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.36341</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.35372</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.42533</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.38974</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.62885</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.38869</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.57235</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.3619</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.9347000000000001</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.93776</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.05765</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.90343</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.7292999999999999</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.9839199999999999</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.46385</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.43307</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.28475</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.33306</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.12014</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.48953</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.42874</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.22793</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.1935</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.47725</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.5014700000000001</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.19312</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.33805</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.72014</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.5388500000000001</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.38547</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.5008</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.84036</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.51267</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.63229</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.55141</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.97073</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.75464</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.75241</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.76098</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.77012</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.9143300000000001</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.56332</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.80243</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.60029</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.82892</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.2688</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.27241</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.30305</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.74243</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.26926</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.3731</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.45633</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.9619500000000001</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8053400000000001</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8570399999999999</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.85425</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.18638</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.0254</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.7964199999999999</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.605</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33811</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.48624</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.64955</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.47685</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.60627</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.60729</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.47918</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.42057</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.41389</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.39343</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.39197</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.27602</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.36364</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.38957</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.39677</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.83426</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.6966100000000001</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.6372899999999999</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.5955900000000001</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.48764</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.5569299999999999</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.51655</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.5086700000000001</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.81836</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.91995</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.8325499999999999</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.9227799999999999</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.29309</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.28776</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.8436</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.86154</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.6058</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.46098</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.46382</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.51479</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.41061</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.24057</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.47007</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.46164</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.45907</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.53888</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.10715</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.7189099999999999</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.43859</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.46365</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.42472</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.43218</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.42328</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.43643</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.42657</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.44135</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.48709</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.48239</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.48742</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.44969</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.46157</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.39079</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.39278</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.3717</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.40952</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.45987</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.48814</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.5589299999999999</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.91931</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.8685900000000001</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.55823</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.48692</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.00668</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.7036</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.58831</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.9172899999999999</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.74127</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.46554</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.46927</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.45688</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.4142</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.46944</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.36385</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33954</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37038</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.43734</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.41989</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.40141</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.39417</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.38403</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.39021</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.37264</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.38846</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34914</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.36397</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36913</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38105</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.54098</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.59121</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.38181</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.5692</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.85093</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.09132</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.57326</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.79919</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.68872</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.8042999999999999</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.8433999999999999</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.7924500000000001</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.76503</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.7988200000000001</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.77744</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.7668200000000001</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.7699900000000001</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.34372</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.20336</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.48123</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.76052</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.52619</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.77038</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.7782</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.61534</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.7600399999999999</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.63761</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.7735</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.7434700000000001</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.77459</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.07162</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.2347</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.25723</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.3047</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.3715</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.35454</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.4243</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.43675</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.4147</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.9969199999999999</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.8887999999999999</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.85005</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.48116</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.06703</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.82469</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.9108200000000001</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.77567</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.70016</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.6881</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.6962</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.65726</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42421</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.6859400000000001</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.5538999999999999</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40185</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45847</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.58786</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.66004</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.6225000000000001</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36869</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.6931</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40118</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40122</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39188</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37554</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37442</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3773</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36692</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35618</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37103</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39959</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.37206</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.43846</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.69901</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.54734</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.7125199999999999</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.60456</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.60458</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.52046</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.67855</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.68592</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.8482999999999999</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.70782</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.8467899999999999</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.7783600000000001</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.8547899999999999</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.83758</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.83772</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.05026</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.06923</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.8145</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.50725</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.33825</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35198</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.59449</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.29594</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.61822</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.69509</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.67708</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.7380800000000001</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.24962</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.25171</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.54085</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.27254</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.54451</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.52615</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.55814</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.37791</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.30264</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.92722</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.90773</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.58713</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.66055</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.31582</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.31733</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.13976</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.57213</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.66279</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.63797</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.07638</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.04998</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.78162</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.28615</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.26462</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.54078</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.30776</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.30954</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39829</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.6756</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.65887</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.64723</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.39704</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.36946</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37507</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27082</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.37573</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.34526</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.6055499999999999</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.40402</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.36178</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.34449</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.34228</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.33404</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.36293</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.44972</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.33065</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.5939800000000001</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.89806</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.7169800000000001</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.64683</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.6731900000000001</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.83565</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.8577899999999999</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.96946</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.5772999999999999</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.45895</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.26143</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.03037</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.98822</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.69223</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.49216</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.1793</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.4163</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.6113099999999999</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.35894</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.19063</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.67845</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.23295</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.6808500000000001</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.7599199999999999</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.67255</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.33979</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.7752899999999999</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.53761</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.44172</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.85778</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.67863</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.57868</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.7899700000000001</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.63783</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.7669</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.8552999999999999</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.9116299999999999</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.77139</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.78187</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.7699900000000001</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.76335</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.77396</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.11484</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.15342</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.05898</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.07813</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.25816</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.01421</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.04939</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.83269</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.81314</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.8295800000000001</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.8696799999999999</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.8716</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.8528</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.9624400000000001</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.62612</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.59399</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.53813</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.51715</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37851</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37537</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.32367</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.9288500000000001</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.9537</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.24512</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.78089</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.4283</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.45597</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37241</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3921</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.37714</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36386</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37856</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.37258</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38265</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.37227</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.37177</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.36828</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3676</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.38054</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.36046</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.64355</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34809</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.51048</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.60685</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.60853</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.5730499999999999</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.73514</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.62038</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.7406200000000001</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.32311</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.80445</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.88662</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.9949600000000001</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.9823999999999999</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.87893</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.08913</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.83105</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.48418</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.19732</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.4552</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.4056</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.86319</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.5492899999999999</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.85222</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.6056699999999999</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.39823</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.45417</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.53738</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.9841299999999999</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.8033400000000001</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.60425</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.29243</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.87605</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.85946</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.43016</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.2466</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.06098</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.91725</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.88795</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.89434</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.88891</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.91235</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.9133300000000001</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.9513400000000001</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.40027</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.4478</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.55422</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.86758</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.88988</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.8716799999999999</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.9132899999999999</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.71601</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.09825</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.63675</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.61446</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.48791</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.35865</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.00182</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.65298</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.65464</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.45435</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.47528</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.47825</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.45143</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.46482</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41963</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.44557</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.44769</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.4094100000000001</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.40895</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32975</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.40229</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.37405</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3638</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.37403</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.40945</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.39401</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.40816</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.39691</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.7579</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.58809</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.89646</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.18658</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.83769</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.89734</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.39461</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.5575</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.52989</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.41891</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.51101</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>1.26486</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.7085900000000001</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.43634</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.3841</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.41726</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.41223</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.50176</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.5809</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.53599</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.7151000000000001</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.54827</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.4574</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.8757200000000001</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.76197</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.7734800000000001</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.79922</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.8168099999999999</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.59616</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.5668300000000001</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.54644</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.56204</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.5689500000000001</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.5842200000000001</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.65079</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.65323</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.5424800000000001</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.65391</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.65439</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.94192</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.68401</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.57673</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.59166</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.5727599999999999</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.5357000000000001</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.53411</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.6703</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.64062</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.70597</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.57913</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.5318999999999999</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.47947</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.46091</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.4085299999999999</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.4097</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38406</v>
       </c>
     </row>
   </sheetData>
